--- a/光伏配储项目/电价数据/2026/陇田光伏电站.xlsx
+++ b/光伏配储项目/电价数据/2026/陇田光伏电站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.31645</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.25969</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26464</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.24286</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.1608</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.16147</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07266</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.23741</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04712</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17552</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26667</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26967</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26969</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22092</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.20333</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.83443</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.47695</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.18247</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.06422</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.82597</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.00616</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.97672</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7380099999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.95223</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.44214</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.44756</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.46534</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.0458</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.46512</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.45288</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.33079</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.41359</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.13464</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.61425</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.55223</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.18219</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.09307</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.06073</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.76836</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.7838200000000001</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.77864</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.78811</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.7895599999999999</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.78754</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.78889</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.9488799999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.81586</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.59899</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78447</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.78647</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7857000000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.78723</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.43543</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.8379099999999999</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.32752</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.73998</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.74981</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.75967</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.26558</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.17387</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.24926</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.4367200000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.06945999999999999</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.49874</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.49513</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.49832</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5161399999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.43851</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5136499999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6924400000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.49737</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44234</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.40581</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41054</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.33222</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.45412</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.4896</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.47907</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.04783</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.8058</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.11642</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.09744</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.11229</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19279</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.10282</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.09868</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66051</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5022799999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.26295</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>-0.00874</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13346</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26471</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25433</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.2298</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.09568</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26999</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03195</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27489</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42371</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31845</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.10556</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25335</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.05892</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.09221</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19789</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-0.01334</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.02653</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25492</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.04869</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.08752</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.03587</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25109</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21909</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19725</v>
+      </c>
+      <c r="W122" t="n">
+        <v>-0.01444</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17934</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25229</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27336</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20617</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00424</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20175</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04453</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27132</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.18937</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.005849999999999999</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05483</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05482</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31692</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.71284</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22474</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.06470999999999999</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.77119</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91412</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8630599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29609</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88742</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18698</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8702799999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65747</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33078</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03284</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5737899999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2071</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5384</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45589</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43721</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.41701</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.45169</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.5052</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.6051599999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87898</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18421</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26404</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26392</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26373</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32517</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.76751</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.20537</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.08279</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>-0.01382</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.08112</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.01302</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.00027</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.08805</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.01238</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.27415</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.01913</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.44979</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.10144</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.01335</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.03079</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.04314</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>-0.00721</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.01332</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>-0.01067</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.01061</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.03538</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.03622</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.03522</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>-0.03547</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.07585</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>-0.01088</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>-0.01124</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>-0.01297</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>-0.00166</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>-0.01392</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>-0.01221</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>-0.01166</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>-0.00908</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>-0.01373</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>-0.01124</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>-0.01076</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.01013</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.01059</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.08857</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>-0.01132</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.00172</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>-0.00878</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>-0.01073</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>-0.01281</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>-0.00889</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.21593</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>-0.01129</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>-0.01182</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.01077</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.0382</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.01372</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.04674</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-0.01402</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-0.01603</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.0372</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.03791</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-0.02057</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-0.01601</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.00852</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.01782</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-0.0199</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.09358</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-0.009010000000000001</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.08843000000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.0484</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.10537</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.01703</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.04543</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.03931</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.21087</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.25812</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.15079</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>-0.04993</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.07693000000000001</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.14806</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.24013</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.02996</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.0346</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.24068</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.27868</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.24337</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.20339</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.19673</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.21645</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.06108</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.07357999999999999</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.12692</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14093</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.07163</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.20735</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>-0.01035</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.05323</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.02286</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.07864</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.11544</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.03446</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.03554</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.19747</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.04019</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.23811</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.24559</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.03589</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.25623</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.03835</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.06673</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.09212000000000001</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.09179999999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.0892</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.09148999999999999</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.08493000000000001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.07126</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.0829</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.08239</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.07503</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.07167</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.09048</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.08526</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.09006</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.08993999999999999</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.28067</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.10401</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.08595</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.23939</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.07134</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.22947</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>-0.01597</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.07382</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.06570000000000001</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.03628</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.02562</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.05414</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19394</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.03935</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.19098</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.02973</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.05685</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.06411</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.06382</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.07728</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.07579000000000001</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.04054</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.07393000000000001</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.03987</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.01747</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.04049000000000001</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.06988999999999999</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.16844</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.02713</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.14498</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.0324</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.24935</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>-0.04322</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.01128</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.01758</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.15006</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.08439000000000001</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.07183</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.13289</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.25031</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.07293000000000001</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.06765</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.18449</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.13372</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.06795999999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.05936</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.18143</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26766</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.23541</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.27419</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.21705</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.25483</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28593</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27468</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.27467</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28525</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.27455</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27474</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.26651</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25372</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28464</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.25964</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30496</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98951</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6149199999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.47631</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49947</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4407</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.47857</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42173</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.53487</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.40685</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5204800000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41143</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.41813</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.12019</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.10701</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.00218</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.01723</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>-0.01063</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.15561</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6140800000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45775</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.09362999999999999</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.09945999999999999</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.05463</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.08816</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.24665</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>-0.02047</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.04894</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.02055</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.20298</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27309</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20497</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19523</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26932</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27592</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26789</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19794</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19548</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16051</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23844</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.20004</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>8.999999999999999e-05</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19548</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20156</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.01993</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.2084</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17445</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16587</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.16905</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.20499</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.23936</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.21346</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.26588</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.24633</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.24659</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.007019999999999999</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.24954</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.23042</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28228</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.22956</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.23217</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.21075</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.24065</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.22396</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.27314</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.23932</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.20223</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.19814</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.07264</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.18809</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.23058</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.25545</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.15361</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.24818</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.22881</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.26217</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.27382</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27415</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.27894</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.22073</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.21092</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.0007199999999999999</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.24017</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31898</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00057</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28837</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5423300000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.50819</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29933</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41263</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44169</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49877</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.57992</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5518500000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5865499999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.73446</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46501</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42485</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31623</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.27378</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.03194</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.22034</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.20973</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.27378</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5328999999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64806</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32903</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27965</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.18724</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.1922</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.04248</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.25831</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.00114</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.0462</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.04758</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.03487</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>-0.03234</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.19961</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>-0.04095</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.26012</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.20029</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.22397</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.04593999999999999</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.10346</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.26038</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>-0.01615</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.02567</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.02562</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.02359</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.05829</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.05041</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.02596</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.17656</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.007019999999999999</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.007730000000000001</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.03442</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.02444</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.02556</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.02641</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.11831</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.18302</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.11574</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.26996</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.20281</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17456</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01463</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.23774</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.01177</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.01111</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17411</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.00063</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20529</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.28005</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17457</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.008619999999999999</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.1639</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.00024</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16615</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16895</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17176</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17457</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.00694</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.01711</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.18579</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.1561</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.24005</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.03885</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24558</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.06192</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.10852</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.14568</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.26278</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.02557</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.25225</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.16205</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00213</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.00434</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.00012</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.00082</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.19593</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.1925</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.12868</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.00465</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.00131</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.00399</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.00322</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.00321</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.00252</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.004070000000000001</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.00444</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.17074</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.15108</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.20169</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.20009</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.02342</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.11472</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.15011</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.00429</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.01932</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.00423</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.04675</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.05558</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25128</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.03025</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.20985</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.23192</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.22843</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.09965</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.10918</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.23191</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.20908</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.03114</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.02618</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.20015</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.21619</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.23802</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.25501</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05526</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19251</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18922</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.27128</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.00078</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20804</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22822</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21829</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04375</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.00053</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20087</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18096</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.01248</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.01251</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.00155</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24548</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03671</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.006690000000000001</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-7.000000000000001e-05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04865</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02166</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02675</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03881</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.22887</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.10765</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20601</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.20783</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.21356</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.20856</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.20972</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.19066</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24555</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25904</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.24887</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.22177</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.27753</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27194</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.03267</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17698</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17148</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17592</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17322</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.02076</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.16927</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15769</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.02006</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.04919</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.02221</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.01952</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.00842</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.01053</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20039</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20015</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.04814</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85711</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08467</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.00343</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25533</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00169</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06666</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47061</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.6426900000000001</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.49571</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.72302</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.77567</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.55606</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.42941</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.58123</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.70098</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.70098</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.6998300000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.77399</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.42707</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31256</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27559</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26897</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.19986</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26281</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25946</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22097</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.26847</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20809</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17485</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.2036</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16927</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17168</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.02075</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.16745</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18981</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23949</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27133</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22069</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23872</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.22776</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29652</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4441000000000001</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.45457</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.27855</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.71765</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.73565</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.49514</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.64034</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.7361799999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31994</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.26028</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.54977</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.26921</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7464</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.65444</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.54808</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32685</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.01945</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19571</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.41437</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.53104</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.09655</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.13882</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.44084</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3323</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.65374</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.13428</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.25079</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.15029</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.07041</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.34169</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.23004</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17909</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14638</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.20101</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14204</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.11622</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22593</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26668</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14331</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18851</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.26775</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22999</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.04514</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04685</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.09587999999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.02349</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.09916</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.21006</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.27031</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.19943</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.11766</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.07875</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>-0.00764</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.23966</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.14893</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.25956</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.23882</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>-0.03869</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.23533</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.33297</v>
       </c>
     </row>
   </sheetData>
